--- a/template.xlsx
+++ b/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Python練習\檔案\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C0EBAC-C6EA-43E3-A0B1-96BA2E53FCC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{946AEBF6-722A-4D42-8F4E-30948A31FB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>NewName</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -61,10 +61,6 @@
   </si>
   <si>
     <t>D:\user\01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>C:\Users\user\</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -91,6 +87,73 @@
   </si>
   <si>
     <r>
+      <t>New Folder Path</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 新路徑</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B011</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">File </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>原始檔名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(含副檔名)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\user\02\D01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>02.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\user\02\D02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">NewName </t>
     </r>
     <r>
@@ -105,60 +168,17 @@
       </rPr>
       <t>修改後檔名</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>New Folder Path</t>
-    </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FFFF0000"/>
+        <color theme="1"/>
         <rFont val="新細明體"/>
         <family val="1"/>
         <charset val="136"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 新路徑</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B011</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">File </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>原始檔名</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(含副檔名)</t>
+      <t>(不寫副檔名)</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -584,7 +604,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{914C88FA-FCCB-4012-B6D3-2F15095E3745}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.42578125" customWidth="1"/>
@@ -595,16 +615,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -615,7 +635,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -623,26 +643,42 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="2tJyg7uHgGj1maznVJNaU2ZF/SEVRL/0TLpydTgNSIoso1eDKXhZKzz1Jyq3TdmH4sMT1WM92/hOGHAatQ0FHA==" saltValue="+V1e/nwnCiPlW2Gy9eqZog==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="dFphx/gSkRPd2tjA5i2P5R+mK2IJSa4f9PvLygkqDL1M/BFsopKT9aUWWdqk8zl8I64IT0zW87auAdG9vldAQA==" saltValue="DTDHACXQHnALckDGp0QlOg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange algorithmName="SHA-512" hashValue="uaoKM0mS/av+QPkyqoenhgEDua8pQyp9dd7BE6Qlb0mSlZaJtTnWbrUuRDgiWHi9Tvy9sZWDKD9C3qlKms3Pew==" saltValue="K5cw5JFgMs/2syoYegB5Zg==" spinCount="100000" sqref="A1:D1" name="範圍1_1"/>
   </protectedRanges>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" sqref="A1 D1 C1" xr:uid="{37603CE5-5CF2-40FF-94F4-22AAACBE7D7B}"/>
+    <dataValidation allowBlank="1" sqref="A1 C1:D1" xr:uid="{37603CE5-5CF2-40FF-94F4-22AAACBE7D7B}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/template.xlsx
+++ b/template.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Python練習\檔案\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python-test\movetofolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{946AEBF6-722A-4D42-8F4E-30948A31FB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF998CBB-FBBF-48E8-A722-86AF9A19D432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="0clwoZgohi1ebTirl42QWosCUfhswrsa/tNHW0KItugYYs6ps69QQ1O5soQcwKRW3EgeRPgeIW/uBmeqs7F9+Q==" workbookSaltValue="yqvg+kzMVI8k9F/ZDYrplQ==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,11 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
-  <si>
-    <t>NewName</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
   <si>
     <t>File Path</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -112,6 +109,42 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>02.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>New Name</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\Downloads\D02-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改檔名+搬移</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>相同檔案複製到多個資料夾</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>搬移檔案+新建資料夾</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\Documents\02\A01-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>資料夾搬移到新資料夾</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\Folder\D01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">File </t>
     </r>
@@ -125,10 +158,28 @@
         <charset val="136"/>
         <scheme val="minor"/>
       </rPr>
-      <t>原始檔名</t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">原始檔名 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(含副檔名)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">New Name </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="新細明體"/>
@@ -136,25 +187,70 @@
         <charset val="136"/>
         <scheme val="minor"/>
       </rPr>
-      <t>(含副檔名)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>D:\user\02\D01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>02.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>D:\user\02\D02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">NewName </t>
+      <t xml:space="preserve">新檔名
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(不要寫副檔名)   (不要寫副檔名)   (不要寫副檔名)  </t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\Documents\02\A02-1\Word</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新建資料夾</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>New Folder Path2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>New Folder Path3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>直接收改資料夾名稱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\Folder</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>New Folder Path</t>
     </r>
     <r>
       <rPr>
@@ -166,28 +262,97 @@
         <charset val="136"/>
         <scheme val="minor"/>
       </rPr>
-      <t>修改後檔名</t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(不寫副檔名)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>New Folder Path</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>搬到新路徑底下當子資料夾</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\113</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\114</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\Downloads\課本01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\Downloads\課本01(保留)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Rename Folder </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是否修改原資料夾名稱</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rename Folder</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -221,23 +386,62 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
       <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -245,15 +449,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -556,129 +782,199 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.5703125" customWidth="1"/>
-    <col min="2" max="2" width="49" customWidth="1"/>
+    <col min="1" max="1" width="31.85546875" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" customWidth="1"/>
     <col min="3" max="3" width="36" customWidth="1"/>
-    <col min="4" max="4" width="37.140625" customWidth="1"/>
+    <col min="4" max="4" width="27.7109375" customWidth="1"/>
+    <col min="5" max="5" width="27.85546875" customWidth="1"/>
+    <col min="6" max="6" width="33.140625" customWidth="1"/>
+    <col min="7" max="7" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
+      <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange algorithmName="SHA-512" hashValue="uaoKM0mS/av+QPkyqoenhgEDua8pQyp9dd7BE6Qlb0mSlZaJtTnWbrUuRDgiWHi9Tvy9sZWDKD9C3qlKms3Pew==" saltValue="K5cw5JFgMs/2syoYegB5Zg==" spinCount="100000" sqref="A1:D1" name="範圍1"/>
+    <protectedRange algorithmName="SHA-512" hashValue="uaoKM0mS/av+QPkyqoenhgEDua8pQyp9dd7BE6Qlb0mSlZaJtTnWbrUuRDgiWHi9Tvy9sZWDKD9C3qlKms3Pew==" saltValue="K5cw5JFgMs/2syoYegB5Zg==" spinCount="100000" sqref="A1:F1" name="範圍1"/>
   </protectedRanges>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="4">
-    <dataValidation type="custom" showErrorMessage="1" errorTitle="不可修改標題" sqref="A1" xr:uid="{CDD509AA-C058-4467-BC6F-7F24C1A672B9}">
-      <formula1>"File Path"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" showErrorMessage="1" errorTitle="不可修改標題" sqref="B1" xr:uid="{F5B484FE-E506-42A5-9FA7-90CB836D4C93}">
-      <formula1>"File"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" showErrorMessage="1" errorTitle="不可修改標題" sqref="C1" xr:uid="{AC66113D-A8E1-46A6-8091-4CC5C1184CAC}">
-      <formula1>"NewName"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" showErrorMessage="1" sqref="D1" xr:uid="{6CF9D1B2-7001-4612-9800-24830C0F073D}">
-      <formula1>"New Folder Path"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{914C88FA-FCCB-4012-B6D3-2F15095E3745}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.140625" customWidth="1"/>
-    <col min="3" max="3" width="38.5703125" customWidth="1"/>
-    <col min="4" max="4" width="29.5703125" customWidth="1"/>
+    <col min="1" max="1" width="32.42578125" customWidth="1"/>
+    <col min="2" max="2" width="32.28515625" customWidth="1"/>
+    <col min="3" max="3" width="30.140625" customWidth="1"/>
+    <col min="4" max="4" width="31.42578125" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="6" max="6" width="21.140625" customWidth="1"/>
+    <col min="7" max="7" width="37.140625" customWidth="1"/>
+    <col min="8" max="8" width="32.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
+    <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
+    <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D5" t="s">
-        <v>15</v>
+    <row r="8" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="dFphx/gSkRPd2tjA5i2P5R+mK2IJSa4f9PvLygkqDL1M/BFsopKT9aUWWdqk8zl8I64IT0zW87auAdG9vldAQA==" saltValue="DTDHACXQHnALckDGp0QlOg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
-    <protectedRange algorithmName="SHA-512" hashValue="uaoKM0mS/av+QPkyqoenhgEDua8pQyp9dd7BE6Qlb0mSlZaJtTnWbrUuRDgiWHi9Tvy9sZWDKD9C3qlKms3Pew==" saltValue="K5cw5JFgMs/2syoYegB5Zg==" spinCount="100000" sqref="A1:D1" name="範圍1_1"/>
+    <protectedRange algorithmName="SHA-512" hashValue="uaoKM0mS/av+QPkyqoenhgEDua8pQyp9dd7BE6Qlb0mSlZaJtTnWbrUuRDgiWHi9Tvy9sZWDKD9C3qlKms3Pew==" saltValue="K5cw5JFgMs/2syoYegB5Zg==" spinCount="100000" sqref="A1:F1" name="範圍1_1"/>
   </protectedRanges>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" sqref="A1 C1:D1" xr:uid="{37603CE5-5CF2-40FF-94F4-22AAACBE7D7B}"/>
+    <dataValidation allowBlank="1" sqref="A1 C1:F1" xr:uid="{37603CE5-5CF2-40FF-94F4-22AAACBE7D7B}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
